--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-24 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>21.09</v>
+        <v>20.83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>53.07</v>
+        <v>53.63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44</v>
+        <v>44.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20.72</v>
+        <v>20.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>20.97</v>
+        <v>20.88</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.62</v>
+        <v>10.76</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.07</v>
+        <v>12.19</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.53</v>
+        <v>12.65</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.66</v>
+        <v>36.78</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69.01000000000001</v>
+        <v>69.13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-21 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-24 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>21.09</v>
+        <v>20.83</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10395.395072</v>
+        <v>10267.239424</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9936.706560000001</v>
+        <v>9887.415295999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>53.07</v>
+        <v>53.63</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>22003.775488</v>
+        <v>22235.963392</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>20792.481792</v>
+        <v>21272.117248</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>44</v>
+        <v>44.3</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>32423.317504</v>
+        <v>32644.384768</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>30356.600832</v>
+        <v>31262.982144</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.72</v>
+        <v>20.4</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13919.041536</v>
+        <v>13682.532352</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13522.395136</v>
+        <v>13455.217664</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,19 +5135,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.97</v>
+        <v>20.88</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21555.795968</v>
+        <v>21463.281664</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21360.5888</v>
+        <v>21216.677888</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1639.442048</v>
+        <v>1629.442048</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(C7/E7,"n/m")</f>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.62</v>
+        <v>10.76</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3145.054464</v>
+        <v>3186.514688</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3253.505024</v>
+        <v>3149.854464</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.07</v>
+        <v>12.19</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3572.205312</v>
+        <v>3607.720192</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3193.624832</v>
+        <v>3243.937536</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.53</v>
+        <v>12.65</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2771.714816</v>
+        <v>2798.259712</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2723.763712</v>
+        <v>2699.431168</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>36.66</v>
+        <v>36.78</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5280.365568</v>
+        <v>5297.649664</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7000813</v>
+        <v>4.688316</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5256.373248</v>
+        <v>5194.438144</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1256.929024</v>
+        <v>1250.134784</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1154.588288</v>
+        <v>1120.620032</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-24 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-25 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>20.83</v>
+        <v>21.24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>22.58</v>
+        <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>53.63</v>
+        <v>54.21</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44.3</v>
+        <v>43.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20.4</v>
+        <v>20.92</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>20.88</v>
+        <v>21.59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.76</v>
+        <v>11.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.19</v>
+        <v>12.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.65</v>
+        <v>12.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.78</v>
+        <v>38.19</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.36</v>
+        <v>7.49</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69.13</v>
+        <v>69</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-24 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-25 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.83</v>
+        <v>21.24</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10267.239424</v>
+        <v>10469.330944</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9887.415295999999</v>
+        <v>9759.259647999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>53.63</v>
+        <v>54.21</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>22235.963392</v>
+        <v>22476.439552</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21272.117248</v>
+        <v>21505.67936</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>44.3</v>
+        <v>43.7</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>32644.384768</v>
+        <v>32202.25024</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>31262.982144</v>
+        <v>31049.281536</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.4</v>
+        <v>20.92</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13682.532352</v>
+        <v>14031.302656</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13455.217664</v>
+        <v>13240.252416</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.88</v>
+        <v>21.59</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21463.281664</v>
+        <v>22193.117184</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21216.677888</v>
+        <v>21124.165632</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.76</v>
+        <v>11.09</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3186.514688</v>
+        <v>3284.242432</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3149.854464</v>
+        <v>3191.314688</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.19</v>
+        <v>12.45</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3607.720192</v>
+        <v>3684.669184</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3243.937536</v>
+        <v>3279.452672</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.65</v>
+        <v>12.83</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2798.259712</v>
+        <v>2838.076928</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2699.431168</v>
+        <v>2725.975808</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>36.78</v>
+        <v>38.19</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5297.649664</v>
+        <v>5500.740608</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.688316</v>
+        <v>4.694052</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5194.438144</v>
+        <v>5211.72224</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.36</v>
+        <v>7.49</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1250.134784</v>
+        <v>1272.215936</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1120.620032</v>
+        <v>1113.826432</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-27 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>21.24</v>
+        <v>20.99</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>54.21</v>
+        <v>52.63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>43.7</v>
+        <v>43.41</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20.92</v>
+        <v>20.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.59</v>
+        <v>21.44</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>11.09</v>
+        <v>10.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.45</v>
+        <v>12.41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.83</v>
+        <v>13.07</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.19</v>
+        <v>38.47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.49</v>
+        <v>7.59</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69</v>
+        <v>69.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-25 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-27 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>21.24</v>
+        <v>20.99</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10469.330944</v>
+        <v>10346.104832</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9759.259647999999</v>
+        <v>9838.125056000001</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>54.21</v>
+        <v>52.63</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>22476.439552</v>
+        <v>21821.345792</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21505.67936</v>
+        <v>21088.60416</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>43.7</v>
+        <v>43.41</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>32202.25024</v>
+        <v>31988.549632</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>31049.281536</v>
+        <v>30763.3664</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.92</v>
+        <v>20.7</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>14031.302656</v>
+        <v>13883.747328</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13240.252416</v>
+        <v>13441.782784</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>21.59</v>
+        <v>21.44</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>22193.117184</v>
+        <v>22038.92736</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21124.165632</v>
+        <v>21699.80928</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>11.09</v>
+        <v>10.89</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3284.242432</v>
+        <v>3225.013504</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3191.314688</v>
+        <v>3229.813504</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.45</v>
+        <v>12.41</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3684.669184</v>
+        <v>3672.830976</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3279.452672</v>
+        <v>3344.5632</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.83</v>
+        <v>13.07</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2838.076928</v>
+        <v>2891.166208</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2725.975808</v>
+        <v>2818.88256</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.19</v>
+        <v>38.47</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5500.740608</v>
+        <v>5541.07136</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.694052</v>
+        <v>4.710426</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5211.72224</v>
+        <v>5455.143424</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.49</v>
+        <v>7.59</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1272.215936</v>
+        <v>1289.201536</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1113.826432</v>
+        <v>1152.889856</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-27 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-28 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>20.99</v>
+        <v>21.74</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>52.63</v>
+        <v>54.89</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>43.41</v>
+        <v>42.96</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20.7</v>
+        <v>21.43</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.44</v>
+        <v>22.21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.89</v>
+        <v>11.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.41</v>
+        <v>12.81</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>13.07</v>
+        <v>13.46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.47</v>
+        <v>40.53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.59</v>
+        <v>7.73</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69.3</v>
+        <v>69.63</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-27 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-28 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.99</v>
+        <v>21.74</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10346.104832</v>
+        <v>10715.784192</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9838.125056000001</v>
+        <v>10207.804416</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>52.63</v>
+        <v>54.89</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21821.345792</v>
+        <v>22758.381568</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21088.60416</v>
+        <v>22031.192064</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>43.41</v>
+        <v>42.96</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>31988.549632</v>
+        <v>31656.947712</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>30763.3664</v>
+        <v>30430.291968</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.7</v>
+        <v>21.43</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13883.747328</v>
+        <v>14373.366784</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13441.782784</v>
+        <v>13932.173312</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>21.44</v>
+        <v>22.21</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>22038.92736</v>
+        <v>22830.434304</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21699.80928</v>
+        <v>22491.318272</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.89</v>
+        <v>11.3</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3225.013504</v>
+        <v>3346.432768</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3229.813504</v>
+        <v>3351.232512</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.41</v>
+        <v>12.81</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3672.830976</v>
+        <v>3791.21408</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3344.5632</v>
+        <v>3462.946048</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>13.07</v>
+        <v>13.46</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2891.166208</v>
+        <v>2977.436928</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2818.88256</v>
+        <v>2905.153024</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.47</v>
+        <v>40.53</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5541.07136</v>
+        <v>5837.7856</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.710426</v>
+        <v>4.722126</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5455.143424</v>
+        <v>5751.857664</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.59</v>
+        <v>7.73</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1289.201536</v>
+        <v>1312.981248</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1152.889856</v>
+        <v>1176.667648</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-08-29 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>21.74</v>
+        <v>20.76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>54.89</v>
+        <v>52.87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>42.96</v>
+        <v>42.38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>21.43</v>
+        <v>20.38</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>22.21</v>
+        <v>21.13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>11.3</v>
+        <v>10.76</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.81</v>
+        <v>12.26</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>13.46</v>
+        <v>12.77</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40.53</v>
+        <v>38.85</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.73</v>
+        <v>7.47</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,7 +853,7 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69.63</v>
+        <v>67.09</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-28 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-08-29 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>21.74</v>
+        <v>20.76</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10715.784192</v>
+        <v>10232.736768</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>54.89</v>
+        <v>52.87</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>22758.381568</v>
+        <v>21920.851968</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>22031.192064</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>42.96</v>
+        <v>42.38</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>31656.947712</v>
+        <v>31229.550592</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>21.43</v>
+        <v>20.38</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>14373.366784</v>
+        <v>13690.640384</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>22.21</v>
+        <v>21.13</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>22830.434304</v>
+        <v>21720.264704</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>11.3</v>
+        <v>10.76</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3346.432768</v>
+        <v>3186.514688</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.81</v>
+        <v>12.26</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3791.21408</v>
+        <v>3628.437504</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>13.46</v>
+        <v>12.77</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2977.436928</v>
+        <v>2824.804608</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.53</v>
+        <v>38.85</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5837.7856</v>
+        <v>5595.804672</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.722126</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.73</v>
+        <v>7.47</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1312.981248</v>
+        <v>1268.818816</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-01 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>20.76</v>
+        <v>20.59</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>52.87</v>
+        <v>51.92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20.38</v>
+        <v>19.87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.13</v>
+        <v>20.78</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.76</v>
+        <v>10.71</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.26</v>
+        <v>12.08</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.77</v>
+        <v>12.44</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.85</v>
+        <v>38.66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.47</v>
+        <v>7.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>67.09</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-08-29 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-01 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.76</v>
+        <v>20.59</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10232.736768</v>
+        <v>10148.941824</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>10207.804416</v>
+        <v>9724.756992000001</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>52.87</v>
+        <v>51.92</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21920.851968</v>
+        <v>21526.964224</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.642</v>
+        <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>22031.192064</v>
+        <v>21188.702208</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>42.38</v>
+        <v>43</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>31229.550592</v>
+        <v>31686.422528</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>30430.291968</v>
+        <v>30002.8928</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.38</v>
+        <v>19.87</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13690.640384</v>
+        <v>13327.055872</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13932.173312</v>
+        <v>13226.816512</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>21.13</v>
+        <v>20.78</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21720.264704</v>
+        <v>21360.490496</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>22491.318272</v>
+        <v>21381.148672</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.76</v>
+        <v>10.71</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3186.514688</v>
+        <v>3171.707392</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3351.232512</v>
+        <v>3191.314688</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.26</v>
+        <v>12.08</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3628.437504</v>
+        <v>3575.165184</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3462.946048</v>
+        <v>3300.169472</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.77</v>
+        <v>12.44</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2824.804608</v>
+        <v>2751.806208</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2905.153024</v>
+        <v>2752.520448</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.85</v>
+        <v>38.66</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5595.804672</v>
+        <v>5568.43776</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.722126</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5751.857664</v>
+        <v>5509.877248</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.47</v>
+        <v>7.3</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1268.818816</v>
+        <v>1239.943424</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1176.667648</v>
+        <v>1132.508928</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-01 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-02 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>20.59</v>
+        <v>19.86</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>51.92</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>42.38</v>
+        <v>40.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>19.87</v>
+        <v>19.11</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>20.78</v>
+        <v>20.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.71</v>
+        <v>10.24</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.08</v>
+        <v>11.75</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.44</v>
+        <v>11.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.66</v>
+        <v>36.68</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.3</v>
+        <v>7.01</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>67.29000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-01 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-02 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.59</v>
+        <v>19.86</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10148.941824</v>
+        <v>9789.120512</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9724.756992000001</v>
+        <v>9281.140735999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>51.92</v>
+        <v>50</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21526.964224</v>
+        <v>20730.898432</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21188.702208</v>
+        <v>19991.699456</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>43</v>
+        <v>40.7</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>31686.422528</v>
+        <v>29991.569408</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>30002.8928</v>
+        <v>28422.254592</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>19.87</v>
+        <v>19.11</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13327.055872</v>
+        <v>12817.313792</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.78</v>
+        <v>20.2</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21360.490496</v>
+        <v>20764.286976</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21381.148672</v>
+        <v>20425.168896</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.71</v>
+        <v>10.24</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3171.707392</v>
+        <v>3032.519424</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3191.314688</v>
+        <v>3037.319424</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.08</v>
+        <v>11.75</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3575.165184</v>
+        <v>3477.499136</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.44</v>
+        <v>11.9</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2751.806208</v>
+        <v>2632.354816</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.66</v>
+        <v>36.68</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5568.43776</v>
+        <v>5283.246592</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.722126</v>
+        <v>4.730265</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5509.877248</v>
+        <v>5197.318656</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.3</v>
+        <v>7.01</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1239.943424</v>
+        <v>1190.68544</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1132.508928</v>
+        <v>1054.382016</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-02 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-03 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>19.86</v>
+        <v/>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>50</v>
+        <v/>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.7</v>
+        <v>40.24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>19.11</v>
+        <v/>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>20.2</v>
+        <v/>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.24</v>
+        <v/>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>11.75</v>
+        <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>11.9</v>
+        <v/>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.68</v>
+        <v>39.22</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.01</v>
+        <v/>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.83</v>
+        <v>65.87</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-02 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-03 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.86</v>
+        <v>21.2</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9789.120512</v>
+        <v>10449.615872</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>50</v>
+        <v>51.54</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20730.898432</v>
+        <v>21369.411584</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>19991.699456</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.7</v>
+        <v>40.24</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29991.569408</v>
+        <v>29652.598784</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>19.11</v>
+        <v>20.77</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12817.313792</v>
+        <v>13952.630784</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13226.816512</v>
+        <v>13488.805888</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.2</v>
+        <v>21.42</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>20764.286976</v>
+        <v>22018.367488</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.24</v>
+        <v>11.13</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3032.519424</v>
+        <v>3296.088064</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3037.319424</v>
+        <v>3300.888064</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.75</v>
+        <v>12.26</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3477.499136</v>
+        <v>3628.437504</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.9</v>
+        <v>12.78</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2632.354816</v>
+        <v>2827.016448</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2752.520448</v>
+        <v>2754.732544</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>36.68</v>
+        <v>39.22</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5283.246592</v>
+        <v>5649.09824</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.730265</v>
+        <v>4.714537</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>5197.318656</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.01</v>
+        <v>7.5</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1190.68544</v>
+        <v>1273.914496</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1054.382016</v>
+        <v>1137.604224</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-03 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-04 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.24</v>
+        <v>42.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.22</v>
+        <v>41.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>65.87</v>
+        <v>67.59</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-03 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-04 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>21.2</v>
+        <v>21.39</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10449.615872</v>
+        <v>10543.266816</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9281.140735999999</v>
+        <v>9941.635071999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>51.54</v>
+        <v>52.6</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21369.411584</v>
+        <v>21808.90624</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>19991.699456</v>
+        <v>20633.993216</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.24</v>
+        <v>42.3</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29652.598784</v>
+        <v>31170.596864</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28422.254592</v>
+        <v>28787.017728</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.77</v>
+        <v>21.21</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13952.630784</v>
+        <v>14248.208384</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13488.805888</v>
+        <v>13784.384512</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>21.42</v>
+        <v>21.65</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>22018.367488</v>
+        <v>22254.792704</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>20425.168896</v>
+        <v>21679.249408</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>11.13</v>
+        <v>11.47</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3296.088064</v>
+        <v>3396.777216</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3300.888064</v>
+        <v>3401.577216</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.26</v>
+        <v>12.66</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3628.437504</v>
+        <v>3746.820352</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3300.169472</v>
+        <v>3418.552576</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.78</v>
+        <v>13.11</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2827.016448</v>
+        <v>2900.014592</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2754.732544</v>
+        <v>2827.730688</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.22</v>
+        <v>41.1</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5649.09824</v>
+        <v>5919.885824</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.714537</v>
+        <v>4.7117953</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5197.318656</v>
+        <v>5563.170304</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.5</v>
+        <v>7.69</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1273.914496</v>
+        <v>1306.187008</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-04 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-05 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>42.3</v>
+        <v>44.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>41.1</v>
+        <v>39.97</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>67.59</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-04 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-05 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>21.39</v>
+        <v>20.97</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10543.266816</v>
+        <v>10336.24576</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9941.635071999999</v>
+        <v>9828.267008000001</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>52.6</v>
+        <v>51.34</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21808.90624</v>
+        <v>21286.488064</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.642</v>
+        <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>20633.993216</v>
+        <v>21076.092928</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>42.3</v>
+        <v>44.5</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>31170.596864</v>
+        <v>32791.762944</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28787.017728</v>
+        <v>29943.94112</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>21.21</v>
+        <v>20.68</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>14248.208384</v>
+        <v>13870.331904</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13784.384512</v>
+        <v>13428.34688</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>21.65</v>
+        <v>21.24</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>22254.792704</v>
+        <v>21833.33888</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21679.249408</v>
+        <v>21494.2208</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>11.47</v>
+        <v>11.12</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3396.777216</v>
+        <v>3293.126656</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3401.577216</v>
+        <v>3297.926656</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.66</v>
+        <v>12.31</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3746.820352</v>
+        <v>3643.235328</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3418.552576</v>
+        <v>3314.967552</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>13.11</v>
+        <v>12.48</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2900.014592</v>
+        <v>2760.654592</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2827.730688</v>
+        <v>2688.370688</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>41.1</v>
+        <v>39.97</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5919.885824</v>
+        <v>5757.125632</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7117953</v>
+        <v>4.6929517</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5563.170304</v>
+        <v>5833.9584</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.69</v>
+        <v>7.33</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1306.187008</v>
+        <v>1245.039104</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1137.604224</v>
+        <v>1108.731136</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-05 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-08 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v/>
+        <v>20.97</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v/>
+        <v>51.34</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44.5</v>
+        <v>42.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v/>
+        <v>20.68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v/>
+        <v>21.24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v/>
+        <v>11.12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v/>
+        <v>12.31</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v/>
+        <v>12.48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v/>
+        <v>7.33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>66.81999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-05 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-08 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -5036,10 +5036,10 @@
         <v>21286.488064</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21076.092928</v>
+        <v>20550.578176</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>44.5</v>
+        <v>42.7</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>32791.762944</v>
+        <v>31465.355264</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>29943.94112</v>
+        <v>30238.69952</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5103,7 +5103,7 @@
         <v>20.68</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13870.331904</v>
+        <v>13892.171776</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
@@ -5281,10 +5281,10 @@
         <v>5757.125632</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.6929517</v>
+        <v>4.7107716</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5833.9584</v>
+        <v>5671.197696</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-08 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-09 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>20.97</v>
+        <v/>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>51.34</v>
+        <v/>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20.68</v>
+        <v/>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.24</v>
+        <v/>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>11.12</v>
+        <v/>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.31</v>
+        <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12.48</v>
+        <v/>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.97</v>
+        <v>40.16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.33</v>
+        <v/>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>67.06999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-08 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-09 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.97</v>
+        <v>20.75</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10336.24576</v>
+        <v>10227.807232</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9828.267008000001</v>
+        <v>9719.827456000001</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>51.34</v>
+        <v>51</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21286.488064</v>
+        <v>21145.51808</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>20550.578176</v>
+        <v>20408.774656</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>42.7</v>
+        <v>44.5</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>31465.355264</v>
+        <v>32791.762944</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>30238.69952</v>
+        <v>29096.513536</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.68</v>
+        <v>20.46</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13892.171776</v>
+        <v>13744.381952</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>21.24</v>
+        <v>20.66</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21833.33888</v>
+        <v>21237.137408</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>11.12</v>
+        <v>11.13</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3293.126656</v>
+        <v>3296.088064</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3297.926656</v>
+        <v>3300.888064</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.31</v>
+        <v>12.16</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3643.235328</v>
+        <v>3598.8416</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.48</v>
+        <v>12.43</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2760.654592</v>
+        <v>2749.594368</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.97</v>
+        <v>40.16</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5757.125632</v>
+        <v>5784.492032</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7107716</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5671.197696</v>
+        <v>5698.564608</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1245.039104</v>
+        <v>1239.943424</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1108.731136</v>
+        <v>1103.635968</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-09 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-10 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>42.7</v>
+        <v>41.15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40.16</v>
+        <v>41.27</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>66.39</v>
+        <v>67.97</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-09 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-10 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.75</v>
+        <v>21.18</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10227.807232</v>
+        <v>10439.7568</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9719.827456000001</v>
+        <v>9931.777024000001</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>51</v>
+        <v>52.9</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21145.51808</v>
+        <v>21933.29152</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.642</v>
+        <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>20408.774656</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>44.5</v>
+        <v>41.15</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>32791.762944</v>
+        <v>30323.171328</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.46</v>
+        <v>20.85</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13744.381952</v>
+        <v>13984.35328</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13428.34688</v>
+        <v>13542.547456</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.66</v>
+        <v>21</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21237.137408</v>
+        <v>21586.634752</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21494.2208</v>
+        <v>21247.516672</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>11.13</v>
+        <v>11.15</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3296.088064</v>
+        <v>3302.01088</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.16</v>
+        <v>12.33</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3598.8416</v>
+        <v>3649.154304</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3314.967552</v>
+        <v>3320.886528</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.43</v>
+        <v>12.55</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2749.594368</v>
+        <v>2776.139264</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2688.370688</v>
+        <v>2703.855104</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.16</v>
+        <v>41.27</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5784.492032</v>
+        <v>5944.372224</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7107716</v>
+        <v>4.6981997</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>5698.564608</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1239.943424</v>
+        <v>1250.134784</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1103.635968</v>
+        <v>1113.826432</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-10 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-11 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>41.15</v>
+        <v>40.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>41.27</v>
+        <v>39.32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>67.97</v>
+        <v>63.97</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-10 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-11 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>21.18</v>
+        <v>20.15</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10439.7568</v>
+        <v>9932.06272</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>52.9</v>
+        <v>50.65</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21933.29152</v>
+        <v>21000.400896</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>20408.774656</v>
+        <v>21201.215488</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>41.15</v>
+        <v>40.1</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>30323.171328</v>
+        <v>29549.430784</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>29096.513536</v>
+        <v>28285.929472</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.85</v>
+        <v>20.02</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13984.35328</v>
+        <v>13448.804352</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13542.547456</v>
+        <v>12984.98048</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>21</v>
+        <v>20.34</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21586.634752</v>
+        <v>20908.197888</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>11.15</v>
+        <v>10.52</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3302.01088</v>
+        <v>3115.440128</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3300.888064</v>
+        <v>3120.239872</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.33</v>
+        <v>12.05</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3649.154304</v>
+        <v>3566.286336</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3320.886528</v>
+        <v>3238.01856</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.55</v>
+        <v>12.12</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2776.139264</v>
+        <v>2681.020416</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2703.855104</v>
+        <v>2608.736512</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>41.27</v>
+        <v>39.32</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5944.372224</v>
+        <v>5663.501824</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.6981997</v>
+        <v>4.698135</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5698.564608</v>
+        <v>5577.573888</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.36</v>
+        <v>7.12</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1250.134784</v>
+        <v>1209.369472</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-11 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-12 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.1</v>
+        <v>40.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.32</v>
+        <v>38.76</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>63.97</v>
+        <v>65.02</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-11 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-12 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.15</v>
+        <v>19.56</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9932.06272</v>
+        <v>9641.248767999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9931.777024000001</v>
+        <v>9133.268991999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>50.65</v>
+        <v>50.34</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21000.400896</v>
+        <v>20871.868416</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>21201.215488</v>
+        <v>20133.505024</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.1</v>
+        <v>40.05</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29549.430784</v>
+        <v>29512.587264</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28285.929472</v>
+        <v>28989.663232</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>20.02</v>
+        <v>19.78</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13448.804352</v>
+        <v>13287.580672</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.34</v>
+        <v>20.58</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>20908.197888</v>
+        <v>21154.902016</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>21247.516672</v>
+        <v>20815.783936</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.52</v>
+        <v>10.18</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3115.440128</v>
+        <v>3014.750976</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.05</v>
+        <v>11.99</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3566.286336</v>
+        <v>3548.528896</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.12</v>
+        <v>11.91</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2681.020416</v>
+        <v>2634.567168</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.32</v>
+        <v>38.76</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5663.501824</v>
+        <v>5582.841344</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.698135</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5577.573888</v>
+        <v>5496.91392</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>7.12</v>
+        <v>6.49</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1209.369472</v>
+        <v>1102.360576</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1113.826432</v>
+        <v>966.064704</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-12 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-15 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.05</v>
+        <v>39.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.76</v>
+        <v>37.42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>65.02</v>
+        <v>63.51</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-12 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-15 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.56</v>
+        <v>18.8</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9641.248767999999</v>
+        <v>9266.638848000001</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9133.268991999999</v>
+        <v>8758.660096</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>50.34</v>
+        <v>48.64</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20871.868416</v>
+        <v>20167.018496</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>20133.505024</v>
+        <v>19424.479232</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.05</v>
+        <v>39.25</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29512.587264</v>
+        <v>28923.072512</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28989.663232</v>
+        <v>27770.103808</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>19.78</v>
+        <v>18.82</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>13287.580672</v>
+        <v>12642.681856</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>12984.98048</v>
+        <v>12178.857984</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.58</v>
+        <v>19.88</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21154.902016</v>
+        <v>20435.347456</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>20815.783936</v>
+        <v>20096.229376</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.18</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3014.750976</v>
+        <v>2878.524416</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3120.239872</v>
+        <v>2883.324416</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.99</v>
+        <v>11.63</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3548.528896</v>
+        <v>3441.984256</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3238.01856</v>
+        <v>3113.71648</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.91</v>
+        <v>11.44</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2634.567168</v>
+        <v>2530.599936</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2608.736512</v>
+        <v>2458.316288</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.76</v>
+        <v>37.42</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5582.841344</v>
+        <v>5389.832704</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.698135</v>
+        <v>4.717236</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5496.91392</v>
+        <v>5303.90528</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.49</v>
+        <v>6.23</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1102.360576</v>
+        <v>1058.198272</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-15 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-16 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39.25</v>
+        <v>39.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.42</v>
+        <v>37.13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>63.51</v>
+        <v>64.19</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-15 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-16 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.8</v>
+        <v>18.64</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9266.638848000001</v>
+        <v>9187.774464</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8758.660096</v>
+        <v>8679.794688</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>48.64</v>
+        <v>48.42</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20167.018496</v>
+        <v>20075.802624</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.642</v>
+        <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>19424.479232</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39.25</v>
+        <v>39.35</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>28923.072512</v>
+        <v>28996.7616</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.82</v>
+        <v>18.68</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12642.681856</v>
+        <v>12528.907264</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>12178.857984</v>
+        <v>12084.810752</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>19.88</v>
+        <v>19.91</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>20435.347456</v>
+        <v>20466.184192</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>20096.229376</v>
+        <v>20127.06816</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>9.720000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2878.524416</v>
+        <v>2854.832896</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2883.324416</v>
+        <v>2859.632896</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.63</v>
+        <v>11.64</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3441.984256</v>
+        <v>3444.943872</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3113.71648</v>
+        <v>3116.676096</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.44</v>
+        <v>11.4</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2530.599936</v>
+        <v>2521.751808</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2458.316288</v>
+        <v>2449.467904</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.42</v>
+        <v>37.13</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5389.832704</v>
+        <v>5348.06272</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.717236</v>
+        <v>4.7304626</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>5303.90528</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.23</v>
+        <v>6.14</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1058.198272</v>
+        <v>1042.911296</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>966.064704</v>
+        <v>906.620288</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-16 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-17 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39.35</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.13</v>
+        <v>37.41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.19</v>
+        <v>63.84</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-16 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-17 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.64</v>
+        <v>18.33</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9187.774464</v>
+        <v>9034.973184</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8679.794688</v>
+        <v>8526.993920000001</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>48.42</v>
+        <v>47.56</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20075.802624</v>
+        <v>19719.231488</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>19424.479232</v>
+        <v>18974.040064</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39.35</v>
+        <v>39</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>28996.7616</v>
+        <v>28738.848768</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>27770.103808</v>
+        <v>27681.677312</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.68</v>
+        <v>17.99</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12528.907264</v>
+        <v>12085.113856</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>12084.810752</v>
+        <v>11621.289984</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>19.91</v>
+        <v>18.98</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>20466.184192</v>
+        <v>19510.204416</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>20127.06816</v>
+        <v>19171.088384</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>9.640000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2854.832896</v>
+        <v>2822.256896</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2859.632896</v>
+        <v>2827.056896</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.64</v>
+        <v>11.49</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3444.943872</v>
+        <v>3400.550144</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3116.676096</v>
+        <v>3072.282368</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.4</v>
+        <v>11.18</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2521.751808</v>
+        <v>2473.086464</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2449.467904</v>
+        <v>2400.80256</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.13</v>
+        <v>37.41</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5348.06272</v>
+        <v>5388.39296</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7304626</v>
+        <v>4.717236</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5303.90528</v>
+        <v>5302.465024</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.14</v>
+        <v>5.97</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1042.911296</v>
+        <v>1014.035904</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>906.620288</v>
+        <v>877.747328</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-17 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-18 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39</v>
+        <v>39.23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.41</v>
+        <v>40.31</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>63.84</v>
+        <v>66.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-17 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-18 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.33</v>
+        <v>19.49</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9034.973184</v>
+        <v>9606.745088</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8526.993920000001</v>
+        <v>9098.765312</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>47.56</v>
+        <v>49.62</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19719.231488</v>
+        <v>20573.343744</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39</v>
+        <v>39.23</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>28738.848768</v>
+        <v>28908.335104</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>27681.677312</v>
+        <v>28647.745536</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.99</v>
+        <v>18.96</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12085.113856</v>
+        <v>12736.729088</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11621.289984</v>
+        <v>12272.905216</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>18.98</v>
+        <v>19.98</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19510.204416</v>
+        <v>20538.140672</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>19171.088384</v>
+        <v>20199.022592</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>9.529999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2822.256896</v>
+        <v>3011.789312</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2827.056896</v>
+        <v>3016.589312</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.49</v>
+        <v>11.92</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3400.550144</v>
+        <v>3527.81184</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3072.282368</v>
+        <v>3199.544064</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.18</v>
+        <v>12.15</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2473.086464</v>
+        <v>2687.656448</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2400.80256</v>
+        <v>2615.372544</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.41</v>
+        <v>40.31</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5388.39296</v>
+        <v>5806.09792</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.717236</v>
+        <v>4.7605724</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5302.465024</v>
+        <v>5720.169984</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.97</v>
+        <v>6.29</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1014.035904</v>
+        <v>1068.389632</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>877.747328</v>
+        <v>932.096448</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-18 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-19 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39.23</v>
+        <v>40.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40.31</v>
+        <v>40.27</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>66.14</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-18 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-19 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.49</v>
+        <v>19.84</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9606.745088</v>
+        <v>9779.262463999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9098.765312</v>
+        <v>9271.282687999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>49.62</v>
+        <v>49.99</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20573.343744</v>
+        <v>20726.75328</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18974.040064</v>
+        <v>19987.529728</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39.23</v>
+        <v>40.4</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>28908.335104</v>
+        <v>29770.502144</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.96</v>
+        <v>18.92</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12736.729088</v>
+        <v>12709.859328</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>19.98</v>
+        <v>19.76</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>20538.140672</v>
+        <v>20311.994368</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>20199.022592</v>
+        <v>19972.878336</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.17</v>
+        <v>10.21</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3011.789312</v>
+        <v>3023.6352</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3016.589312</v>
+        <v>3028.4352</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.92</v>
+        <v>11.95</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3527.81184</v>
+        <v>3536.690688</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.15</v>
+        <v>11.94</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2687.656448</v>
+        <v>2641.2032</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.31</v>
+        <v>40.27</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5806.09792</v>
+        <v>5800.336384</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7605724</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1068.389632</v>
+        <v>1083.676544</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>932.096448</v>
+        <v>947.382144</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-22 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.4</v>
+        <v>40.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40.27</v>
+        <v>40.24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-19 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-22 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.84</v>
+        <v>19.31</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9779.262463999999</v>
+        <v>9518.021632</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9271.282687999999</v>
+        <v>9010.041856</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>49.99</v>
+        <v>48.75</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20726.75328</v>
+        <v>20212.627456</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>19987.529728</v>
+        <v>19470.35648</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.4</v>
+        <v>40.25</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29770.502144</v>
+        <v>29659.96544</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28647.745536</v>
+        <v>28197.502976</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.92</v>
+        <v>18.35</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12709.859328</v>
+        <v>12326.950912</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>12272.905216</v>
+        <v>11863.12704</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>19.76</v>
+        <v>19.52</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>20311.994368</v>
+        <v>20065.29024</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>19972.878336</v>
+        <v>19726.17216</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.21</v>
+        <v>10.13</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3023.6352</v>
+        <v>2999.94368</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3028.4352</v>
+        <v>3004.74368</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.95</v>
+        <v>11.76</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3536.690688</v>
+        <v>3480.458752</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3199.544064</v>
+        <v>3152.190976</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.94</v>
+        <v>11.83</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2641.2032</v>
+        <v>2616.870656</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2615.372544</v>
+        <v>2544.586752</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.27</v>
+        <v>40.24</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5800.336384</v>
+        <v>5796.015104</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7605724</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5720.169984</v>
+        <v>5710.087168</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.38</v>
+        <v>6.18</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1083.676544</v>
+        <v>1049.705472</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>947.382144</v>
+        <v>913.413952</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-22 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-23 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40.25</v>
+        <v>40</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40.24</v>
+        <v>42.68</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>67.94</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-22 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-23 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.31</v>
+        <v>20.32</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9518.021632</v>
+        <v>10015.857664</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9010.041856</v>
+        <v>9507.877888000001</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>48.75</v>
+        <v>50.85</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>20212.627456</v>
+        <v>21083.324416</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>19470.35648</v>
+        <v>20346.212352</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40.25</v>
+        <v>40</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29659.96544</v>
+        <v>29475.741696</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>28197.502976</v>
+        <v>29350.742016</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.35</v>
+        <v>19.03</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12326.950912</v>
+        <v>12783.75424</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11863.12704</v>
+        <v>12319.929344</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>19.52</v>
+        <v>20.49</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>20065.29024</v>
+        <v>21062.387712</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>19726.17216</v>
+        <v>20723.269632</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.13</v>
+        <v>10.51</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2999.94368</v>
+        <v>3112.478464</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3004.74368</v>
+        <v>3117.278464</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.76</v>
+        <v>12.21</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3480.458752</v>
+        <v>3613.63968</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3152.190976</v>
+        <v>3285.371648</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.83</v>
+        <v>12.34</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2616.870656</v>
+        <v>2729.68576</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2544.586752</v>
+        <v>2657.401856</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.24</v>
+        <v>42.68</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5796.015104</v>
+        <v>6147.463168</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7605724</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5710.087168</v>
+        <v>6061.535744</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.18</v>
+        <v>6.49</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1049.705472</v>
+        <v>1102.360576</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>913.413952</v>
+        <v>966.064704</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-23 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-24 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>42.68</v>
+        <v>39.72</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>67.94</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-23 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-24 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>20.32</v>
+        <v>19.05</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10015.857664</v>
+        <v>9389.865984</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>9507.877888000001</v>
+        <v>8881.886208</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>50.85</v>
+        <v>48.11</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>21083.324416</v>
+        <v>19947.272192</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>20346.212352</v>
+        <v>19203.4304</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29475.741696</v>
+        <v>28738.848768</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>29350.742016</v>
+        <v>27143.743488</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>19.03</v>
+        <v>18.27</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12783.75424</v>
+        <v>12273.209344</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>12319.929344</v>
+        <v>11809.385472</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>20.49</v>
+        <v>19.32</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>21062.387712</v>
+        <v>19859.703808</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>20723.269632</v>
+        <v>19520.585728</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>10.51</v>
+        <v>9.26</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3112.478464</v>
+        <v>2742.297856</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>3117.278464</v>
+        <v>2747.097856</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>12.21</v>
+        <v>11.66</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3613.63968</v>
+        <v>3450.862848</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3285.371648</v>
+        <v>3122.595072</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>12.34</v>
+        <v>11.51</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2729.68576</v>
+        <v>2546.084608</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2657.401856</v>
+        <v>2473.800704</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>42.68</v>
+        <v>39.72</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>6147.463168</v>
+        <v>5721.116672</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7605724</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>6061.535744</v>
+        <v>5635.188736</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.49</v>
+        <v>6.04</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1102.360576</v>
+        <v>1025.92576</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>966.064704</v>
+        <v>889.63616</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-24 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-25 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39</v>
+        <v>37.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.72</v>
+        <v>39.57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.68000000000001</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-24 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-25 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.05</v>
+        <v>18.76</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9389.865984</v>
+        <v>9246.923776</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8881.886208</v>
+        <v>8738.944</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>48.11</v>
+        <v>47.51</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19947.272192</v>
+        <v>19698.499584</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>19203.4304</v>
+        <v>18953.18528</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39</v>
+        <v>37.25</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>28738.848768</v>
+        <v>27449.284608</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>27143.743488</v>
+        <v>26244.732928</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.27</v>
+        <v>17.94</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12273.209344</v>
+        <v>12051.526656</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11809.385472</v>
+        <v>11587.70176</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>19.32</v>
+        <v>18.94</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19859.703808</v>
+        <v>19469.088768</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>19520.585728</v>
+        <v>19129.970688</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>9.26</v>
+        <v>9.16</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2742.297856</v>
+        <v>2712.683264</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2747.097856</v>
+        <v>2717.48352</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.66</v>
+        <v>11.5</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3450.862848</v>
+        <v>3403.50976</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3122.595072</v>
+        <v>3075.241984</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.51</v>
+        <v>11.34</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2546.084608</v>
+        <v>2508.479488</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2473.800704</v>
+        <v>2436.195584</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.72</v>
+        <v>39.57</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5721.116672</v>
+        <v>5699.510784</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7605724</v>
+        <v>4.8002596</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5635.188736</v>
+        <v>5613.58336</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6.04</v>
+        <v>5.91</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1025.92576</v>
+        <v>1003.844608</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>889.63616</v>
+        <v>867.556864</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-25 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-26 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37.25</v>
+        <v>37.28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.57</v>
+        <v>40.34</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.04000000000001</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-25 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-26 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.76</v>
+        <v>19.01</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9246.923776</v>
+        <v>9370.149888</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8738.944</v>
+        <v>8862.170112</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>47.51</v>
+        <v>48.04</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19698.499584</v>
+        <v>19918.247936</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18953.18528</v>
+        <v>19174.234112</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.25</v>
+        <v>37.28</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27449.284608</v>
+        <v>27471.39072</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>26244.732928</v>
+        <v>26532.122624</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.94</v>
+        <v>18.19</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12051.526656</v>
+        <v>12219.4688</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11587.70176</v>
+        <v>11755.643904</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>18.94</v>
+        <v>19.22</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19469.088768</v>
+        <v>19756.908544</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>19129.970688</v>
+        <v>19417.792512</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>9.16</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2712.683264</v>
+        <v>2780.796672</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2717.48352</v>
+        <v>2785.596672</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.5</v>
+        <v>11.69</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3403.50976</v>
+        <v>3459.741696</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3075.241984</v>
+        <v>3131.47392</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.57</v>
+        <v>40.34</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5699.510784</v>
+        <v>5810.418688</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.8002596</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5613.58336</v>
+        <v>5724.491264</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.91</v>
+        <v>5.94</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1003.844608</v>
+        <v>1008.940288</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>867.556864</v>
+        <v>872.652096</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-26 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-29 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v/>
+        <v>17.95</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v/>
+        <v>45.77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37.28</v>
+        <v>36.75</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v/>
+        <v>17.01</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v/>
+        <v>17.87</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v/>
+        <v>8.960000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v/>
+        <v>11.21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v/>
+        <v>10.76</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40.34</v>
+        <v>37.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v/>
+        <v>5.61</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>61.06</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-26 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-29 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>19.01</v>
+        <v>17.95</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>9370.149888</v>
+        <v>8847.669248</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8862.170112</v>
+        <v>8339.689472</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>48.04</v>
+        <v>45.77</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19918.247936</v>
+        <v>18977.06496</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.642</v>
+        <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>19174.234112</v>
+        <v>18227.47648</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.28</v>
+        <v>37.25</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27471.39072</v>
+        <v>27449.284608</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>26532.122624</v>
+        <v>25854.179328</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18.19</v>
+        <v>17.01</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>12219.4688</v>
+        <v>11408.818176</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11755.643904</v>
+        <v>10962.957312</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>19.22</v>
+        <v>17.87</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19756.908544</v>
+        <v>18369.19808</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>19417.792512</v>
+        <v>18030.08</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>9.390000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2780.796672</v>
+        <v>2653.454592</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2785.596672</v>
+        <v>2658.254592</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.69</v>
+        <v>11.21</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3459.741696</v>
+        <v>3317.682176</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3131.47392</v>
+        <v>2989.4144</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>11.34</v>
+        <v>10.76</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2508.479488</v>
+        <v>2380.179968</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2436.195584</v>
+        <v>2307.895808</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.34</v>
+        <v>37.65</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5810.418688</v>
+        <v>5422.961664</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.8002596</v>
+        <v>4.7605724</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5724.491264</v>
+        <v>5337.033728</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.94</v>
+        <v>5.61</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1008.940288</v>
+        <v>952.888064</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>872.652096</v>
+        <v>816.604544</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-29 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-09-30 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.95</v>
+        <v>18.08</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.77</v>
+        <v>46.14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>36.75</v>
+        <v>35.85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.01</v>
+        <v>17.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.87</v>
+        <v>17.84</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>11.21</v>
+        <v>11.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.76</v>
+        <v>10.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.65</v>
+        <v>38.51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.06</v>
+        <v>61.51</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-29 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-09-30 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.95</v>
+        <v>18.08</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8847.669248</v>
+        <v>8911.747072</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8339.689472</v>
+        <v>8403.767296</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.77</v>
+        <v>46.14</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18977.06496</v>
+        <v>19130.474496</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18227.47648</v>
+        <v>18381.795328</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.25</v>
+        <v>36.75</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27449.284608</v>
+        <v>27080.839168</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25854.179328</v>
+        <v>25190.975488</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.01</v>
+        <v>17.15</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11408.818176</v>
+        <v>11502.716928</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10962.957312</v>
+        <v>11057.004544</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.87</v>
+        <v>17.84</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18369.19808</v>
+        <v>18338.359296</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>18030.08</v>
+        <v>17999.243264</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2653.454592</v>
+        <v>2588.302592</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2658.254592</v>
+        <v>2593.102848</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.21</v>
+        <v>11.35</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3317.682176</v>
+        <v>3359.116288</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2989.4144</v>
+        <v>3030.848256</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.76</v>
+        <v>10.83</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2380.179968</v>
+        <v>2395.664128</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2307.895808</v>
+        <v>2323.380224</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.65</v>
+        <v>38.51</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5422.961664</v>
+        <v>5546.832384</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7605724</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5337.033728</v>
+        <v>5460.90496</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>952.888064</v>
+        <v>956.285184</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>816.604544</v>
+        <v>820.001344</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-09-30 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-01 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>18.08</v>
+        <v/>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46.14</v>
+        <v/>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.15</v>
+        <v/>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.84</v>
+        <v/>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.74</v>
+        <v/>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>11.35</v>
+        <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.83</v>
+        <v/>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.51</v>
+        <v>38.31</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.63</v>
+        <v/>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.51</v>
+        <v>60.97</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-09-30 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-01 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>18.08</v>
+        <v>17.69</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8911.747072</v>
+        <v>8719.5136</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8403.767296</v>
+        <v>8211.533824</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>46.14</v>
+        <v>45.51</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19130.474496</v>
+        <v>18869.264384</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18381.795328</v>
+        <v>18119.036928</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>36.75</v>
+        <v>35.85</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27080.839168</v>
+        <v>26417.63328</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25190.975488</v>
+        <v>25930.080256</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.15</v>
+        <v>17.03</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11502.716928</v>
+        <v>11440.217088</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11057.004544</v>
+        <v>10976.392192</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.84</v>
+        <v>17.6</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18338.359296</v>
+        <v>18091.655168</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17999.243264</v>
+        <v>17752.537088</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.74</v>
+        <v>8.58</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2588.302592</v>
+        <v>2540.919552</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2593.102848</v>
+        <v>2545.719552</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.35</v>
+        <v>11.24</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3359.116288</v>
+        <v>3326.560768</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3030.848256</v>
+        <v>2998.292992</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.83</v>
+        <v>10.67</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2395.664128</v>
+        <v>2360.27136</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2323.380224</v>
+        <v>2287.9872</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.51</v>
+        <v>38.31</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5546.832384</v>
+        <v>5518.025728</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7605724</v>
+        <v>4.8002596</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5460.90496</v>
+        <v>5432.097792</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>956.285184</v>
+        <v>942.696768</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>820.001344</v>
+        <v>806.41408</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-01 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-02 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v/>
+        <v>17.66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v/>
+        <v>44.98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.85</v>
+        <v>35.81</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v/>
+        <v>17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v/>
+        <v>17.56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v/>
+        <v>8.56</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v/>
+        <v>11.17</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v/>
+        <v>10.63</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.31</v>
+        <v>38.28</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v/>
+        <v>5.51</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.97</v>
+        <v>60.65</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-01 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-02 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.69</v>
+        <v>17.66</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8719.5136</v>
+        <v>8704.726016000001</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8211.533824</v>
+        <v>8196.746751999999</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.51</v>
+        <v>44.98</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18869.264384</v>
+        <v>18649.516032</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.642</v>
+        <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18119.036928</v>
+        <v>17897.988096</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.85</v>
+        <v>35.81</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26417.63328</v>
+        <v>26388.160512</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25930.080256</v>
+        <v>25213.0816</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.03</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11440.217088</v>
+        <v>11402.110976</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10976.392192</v>
+        <v>10956.238848</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.6</v>
+        <v>17.56</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18091.655168</v>
+        <v>18050.537472</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17752.537088</v>
+        <v>17711.42144</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.58</v>
+        <v>8.56</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2540.919552</v>
+        <v>2534.996992</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2545.719552</v>
+        <v>2539.796736</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.24</v>
+        <v>11.17</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3326.560768</v>
+        <v>3305.843968</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2998.292992</v>
+        <v>2977.575936</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.67</v>
+        <v>10.63</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2360.27136</v>
+        <v>2351.422976</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2287.9872</v>
+        <v>2279.139072</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.31</v>
+        <v>38.28</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5518.025728</v>
+        <v>5513.703936</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.8002596</v>
+        <v>4.7605724</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5432.097792</v>
+        <v>5427.776512</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.55</v>
+        <v>5.51</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>942.696768</v>
+        <v>935.902528</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>806.41408</v>
+        <v>799.620416</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-02 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-03 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.66</v>
+        <v/>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.98</v>
+        <v/>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.81</v>
+        <v>35.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17</v>
+        <v/>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.56</v>
+        <v/>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.56</v>
+        <v/>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>11.17</v>
+        <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.63</v>
+        <v/>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.28</v>
+        <v>38.68</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.51</v>
+        <v/>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.65</v>
+        <v>60.71</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-02 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-03 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.66</v>
+        <v>17.67</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8704.726016000001</v>
+        <v>8709.655552</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8196.746751999999</v>
+        <v>8201.675776</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.98</v>
+        <v>45.51</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18649.516032</v>
+        <v>18869.264384</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17897.988096</v>
+        <v>18119.036928</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.81</v>
+        <v>35.9</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26388.160512</v>
+        <v>26454.480896</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25213.0816</v>
+        <v>25419.411456</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11402.110976</v>
+        <v>11554.417664</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10956.238848</v>
+        <v>11090.592768</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.56</v>
+        <v>17.66</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18050.537472</v>
+        <v>18153.330688</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17711.42144</v>
+        <v>17814.214656</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.56</v>
+        <v>8.6</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2534.996992</v>
+        <v>2546.842624</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2539.796736</v>
+        <v>2551.642624</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.17</v>
+        <v>11.25</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3305.843968</v>
+        <v>3329.520384</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2977.575936</v>
+        <v>3001.252608</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.63</v>
+        <v>10.58</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2351.422976</v>
+        <v>2340.362752</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2279.139072</v>
+        <v>2268.078848</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.28</v>
+        <v>38.68</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5513.703936</v>
+        <v>5571.318784</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.7605724</v>
+        <v>4.8002596</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5427.776512</v>
+        <v>5485.390848</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>935.902528</v>
+        <v>942.696768</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>799.620416</v>
+        <v>806.41408</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-03 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-06 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v/>
+        <v>17.51</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v/>
+        <v>45.32</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.9</v>
+        <v>37.44</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v/>
+        <v>17.01</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v/>
+        <v>17.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v/>
+        <v>8.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v/>
+        <v>11.14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v/>
+        <v>10.55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.68</v>
+        <v>38.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v/>
+        <v>5.58</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.71</v>
+        <v>61.03</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-03 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-06 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.67</v>
+        <v>17.51</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8709.655552</v>
+        <v>8630.790144000001</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8201.675776</v>
+        <v>8122.81088</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.51</v>
+        <v>45.32</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18869.264384</v>
+        <v>18790.486016</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.642</v>
+        <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18119.036928</v>
+        <v>18039.793664</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5074,7 +5074,7 @@
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25419.411456</v>
+        <v>26362.636288</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.2</v>
+        <v>17.01</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11554.417664</v>
+        <v>11408.818176</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11090.592768</v>
+        <v>10962.957312</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.66</v>
+        <v>17.05</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18153.330688</v>
+        <v>17526.290432</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17814.214656</v>
+        <v>17187.1744</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.25</v>
+        <v>11.14</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3329.520384</v>
+        <v>3296.965376</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>3001.252608</v>
+        <v>2968.697344</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.58</v>
+        <v>10.55</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2340.362752</v>
+        <v>2333.726464</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2268.078848</v>
+        <v>2261.44256</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.68</v>
+        <v>38.55</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5571.318784</v>
+        <v>5552.59392</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.8002596</v>
+        <v>4.8489323</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5485.390848</v>
+        <v>5466.666496</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.55</v>
+        <v>5.58</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>942.696768</v>
+        <v>947.792384</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>806.41408</v>
+        <v>811.509312</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-06 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-07 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.51</v>
+        <v>17.54</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.32</v>
+        <v>45.92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37.44</v>
+        <v>36.37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.01</v>
+        <v>17.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.05</v>
+        <v>17.17</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>11.14</v>
+        <v>11.18</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.55</v>
+        <v>10.51</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38.55</v>
+        <v>39.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.58</v>
+        <v>5.57</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.03</v>
+        <v>61.56</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-06 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-07 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.51</v>
+        <v>17.54</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8630.790144000001</v>
+        <v>8645.577728</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8122.81088</v>
+        <v>8137.597952</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.32</v>
+        <v>45.92</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18790.486016</v>
+        <v>19039.256576</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18039.793664</v>
+        <v>18290.038784</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.9</v>
+        <v>37.44</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26454.480896</v>
+        <v>27589.29408</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>26362.636288</v>
+        <v>25573.275648</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.01</v>
+        <v>17.1</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11408.818176</v>
+        <v>11487.241216</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10962.957312</v>
+        <v>11023.41632</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.05</v>
+        <v>17.17</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17526.290432</v>
+        <v>17649.64352</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17187.1744</v>
+        <v>17310.52544</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2546.842624</v>
+        <v>2567.572736</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2551.642624</v>
+        <v>2572.372736</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.14</v>
+        <v>11.18</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3296.965376</v>
+        <v>3308.803584</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2968.697344</v>
+        <v>2980.535552</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.55</v>
+        <v>10.51</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2333.726464</v>
+        <v>2324.878336</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2261.44256</v>
+        <v>2252.594432</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>38.55</v>
+        <v>39.05</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5552.59392</v>
+        <v>5624.61184</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.8489323</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5466.666496</v>
+        <v>5538.684416</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.58</v>
+        <v>5.57</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>947.792384</v>
+        <v>946.093824</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>811.509312</v>
+        <v>809.81088</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-07 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-08 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.54</v>
+        <v>16.65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.92</v>
+        <v>44.35</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>36.37</v>
+        <v>35.26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.1</v>
+        <v>16.39</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.17</v>
+        <v>16.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.67</v>
+        <v>8.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>11.18</v>
+        <v>10.12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.51</v>
+        <v>10.04</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.05</v>
+        <v>37.32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.57</v>
+        <v>5.32</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.56</v>
+        <v>60.51</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-07 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-08 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.54</v>
+        <v>16.65</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8645.577728</v>
+        <v>8206.891008000001</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.92</v>
+        <v>44.35</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19039.256576</v>
+        <v>18388.307968</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.642</v>
+        <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>18290.038784</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.44</v>
+        <v>35.26</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27589.29408</v>
+        <v>25982.865408</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.1</v>
+        <v>16.39</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11487.241216</v>
+        <v>10992.975872</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.17</v>
+        <v>16.5</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17649.64352</v>
+        <v>16960.92672</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.67</v>
+        <v>8.32</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2567.572736</v>
+        <v>2463.92192</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11.18</v>
+        <v>10.12</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3308.803584</v>
+        <v>2995.08864</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.51</v>
+        <v>10.04</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2324.878336</v>
+        <v>2220.91136</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.05</v>
+        <v>37.32</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5624.61184</v>
+        <v>5375.429632</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.8489323</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.57</v>
+        <v>5.32</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>946.093824</v>
+        <v>903.630016</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-09 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.65</v>
+        <v>16.98</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.35</v>
+        <v>45.31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.26</v>
+        <v>35.66</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16.39</v>
+        <v>16.73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.5</v>
+        <v>16.87</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.32</v>
+        <v>8.57</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.12</v>
+        <v>10.61</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.04</v>
+        <v>10.31</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.32</v>
+        <v>37.34</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.32</v>
+        <v>5.46</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.51</v>
+        <v>60.33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-08 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-09 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.65</v>
+        <v>16.98</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8206.891008000001</v>
+        <v>8369.549824</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8137.597952</v>
+        <v>7698.911232</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.35</v>
+        <v>45.31</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18388.307968</v>
+        <v>18786.340864</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.45</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18290.038784</v>
+        <v>17635.231744</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5074,7 +5074,7 @@
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25573.275648</v>
+        <v>24756.207616</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.39</v>
+        <v>16.73</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10992.975872</v>
+        <v>11221.0176</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11023.41632</v>
+        <v>10546.460672</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.5</v>
+        <v>16.87</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16960.92672</v>
+        <v>17341.263872</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17310.52544</v>
+        <v>16621.809664</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.32</v>
+        <v>8.57</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2463.92192</v>
+        <v>2537.958144</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2572.372736</v>
+        <v>2468.722176</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.12</v>
+        <v>10.61</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2995.08864</v>
+        <v>3140.107776</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2980.535552</v>
+        <v>2666.820864</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.04</v>
+        <v>10.31</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2220.91136</v>
+        <v>2280.637184</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2252.594432</v>
+        <v>2148.627456</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.32</v>
+        <v>37.34</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5375.429632</v>
+        <v>5378.310144</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.8489323</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5538.684416</v>
+        <v>5289.501696</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.32</v>
+        <v>5.46</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>903.630016</v>
+        <v>927.409728</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>809.81088</v>
+        <v>767.350592</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-09 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-10 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.98</v>
+        <v>17.28</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.31</v>
+        <v>46.27</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.66</v>
+        <v>37.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16.73</v>
+        <v>17.07</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.87</v>
+        <v>17.13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.57</v>
+        <v>8.65</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.61</v>
+        <v>10.92</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.31</v>
+        <v>10.49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.34</v>
+        <v>39.03</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.46</v>
+        <v>5.55</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.33</v>
+        <v>61.11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-09 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-10 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.98</v>
+        <v>17.28</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8369.549824</v>
+        <v>8520.438271999999</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7698.911232</v>
+        <v>8009.442304</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.31</v>
+        <v>46.27</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18786.340864</v>
+        <v>19184.37376</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>17.45</v>
+        <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17635.231744</v>
+        <v>18436.01408</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.26</v>
+        <v>37.5</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25982.865408</v>
+        <v>27633.508352</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>24756.207616</v>
+        <v>25611.003904</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.73</v>
+        <v>17.07</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11221.0176</v>
+        <v>11467.086848</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10546.460672</v>
+        <v>11003.262976</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.87</v>
+        <v>17.13</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17341.263872</v>
+        <v>17608.525824</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16621.809664</v>
+        <v>17269.407744</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.57</v>
+        <v>8.65</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2537.958144</v>
+        <v>2561.649664</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2468.722176</v>
+        <v>2566.449664</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.61</v>
+        <v>10.92</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3140.107776</v>
+        <v>3231.854592</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2666.820864</v>
+        <v>2903.58656</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.31</v>
+        <v>10.49</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2280.637184</v>
+        <v>2320.454144</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2148.627456</v>
+        <v>2248.17024</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.34</v>
+        <v>39.03</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5378.310144</v>
+        <v>5621.731328</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.8489323</v>
+        <v>4.852348</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5289.501696</v>
+        <v>5535.803392</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.46</v>
+        <v>5.55</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>927.409728</v>
+        <v>942.696768</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>767.350592</v>
+        <v>806.41408</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-10 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-13 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.28</v>
+        <v>16.99</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46.27</v>
+        <v>45.71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37.5</v>
+        <v>36.44</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.07</v>
+        <v>16.84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17.13</v>
+        <v>16.76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.65</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.92</v>
+        <v>10.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.49</v>
+        <v>10.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>61.11</v>
+        <v>60.53</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-10 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-13 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>17.28</v>
+        <v>16.99</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8520.438271999999</v>
+        <v>8377.444352</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8009.442304</v>
+        <v>7866.499584</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>46.27</v>
+        <v>45.71</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>19184.37376</v>
+        <v>18952.187904</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18436.01408</v>
+        <v>18202.451968</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5074,7 +5074,7 @@
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25611.003904</v>
+        <v>25622.05696</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17.07</v>
+        <v>16.84</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11467.086848</v>
+        <v>11312.580608</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11003.262976</v>
+        <v>10848.756736</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17.13</v>
+        <v>16.76</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17608.525824</v>
+        <v>17228.189696</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>17269.407744</v>
+        <v>16889.07264</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.65</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2561.649664</v>
+        <v>2529.07392</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2566.449664</v>
+        <v>2533.87392</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.92</v>
+        <v>10.76</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3231.854592</v>
+        <v>3184.501504</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2903.58656</v>
+        <v>2856.233472</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.49</v>
+        <v>10.3</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2320.454144</v>
+        <v>2278.425088</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2248.17024</v>
+        <v>2206.140928</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>942.696768</v>
+        <v>917.218432</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>806.41408</v>
+        <v>780.93792</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-13 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-14 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.99</v>
+        <v/>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.71</v>
+        <v/>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16.84</v>
+        <v/>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.76</v>
+        <v/>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v/>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.76</v>
+        <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.3</v>
+        <v/>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.03</v>
+        <v>37.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.4</v>
+        <v/>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60.53</v>
+        <v>59.15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-13 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-14 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.99</v>
+        <v>16.33</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8377.444352</v>
+        <v>8052.011008</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7866.499584</v>
+        <v>7541.18144</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>45.71</v>
+        <v>44.53</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18952.187904</v>
+        <v>18462.939136</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>18202.451968</v>
+        <v>17710.30528</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>37.5</v>
+        <v>36.44</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27633.508352</v>
+        <v>26852.401152</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25622.05696</v>
+        <v>25301.508096</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.84</v>
+        <v>16.18</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>11312.580608</v>
+        <v>10869.213184</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10848.756736</v>
+        <v>10405.389312</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.76</v>
+        <v>16.26</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>17228.189696</v>
+        <v>16714.222592</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16889.07264</v>
+        <v>16375.105536</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.539999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2529.07392</v>
+        <v>2440.2304</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2533.87392</v>
+        <v>2445.0304</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.76</v>
+        <v>10.58</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3184.501504</v>
+        <v>3131.228928</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2856.233472</v>
+        <v>2802.961152</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.3</v>
+        <v>10.04</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2278.425088</v>
+        <v>2220.91136</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2206.140928</v>
+        <v>2148.627456</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.03</v>
+        <v>37.3</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5621.731328</v>
+        <v>5372.548608</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.852348</v>
+        <v>4.8599634</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5535.803392</v>
+        <v>5286.621184</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>917.218432</v>
+        <v>883.24736</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>780.93792</v>
+        <v>746.969664</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-14 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-15 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v/>
+        <v>15.25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v/>
+        <v>42.33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>36.44</v>
+        <v>34.11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v/>
+        <v>14.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v/>
+        <v>14.98</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v/>
+        <v>7.83</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v/>
+        <v>10.17</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.3</v>
+        <v>36.13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v/>
+        <v>4.88</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>59.15</v>
+        <v>56.22</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-14 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-15 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.33</v>
+        <v>15.25</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8052.011008</v>
+        <v>7519.483904</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7541.18144</v>
+        <v>7008.84224</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.53</v>
+        <v>42.33</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18462.939136</v>
+        <v>17550.780416</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17710.30528</v>
+        <v>16792.742912</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>36.44</v>
+        <v>34.11</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26852.401152</v>
+        <v>25135.439872</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25301.508096</v>
+        <v>23967.731712</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16.18</v>
+        <v>14.9</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10869.213184</v>
+        <v>9993.614336000001</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>10405.389312</v>
+        <v>9545.525248</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16.26</v>
+        <v>14.98</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16714.222592</v>
+        <v>15398.465536</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>16375.105536</v>
+        <v>15059.34848</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.24</v>
+        <v>7.83</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2440.2304</v>
+        <v>2318.811136</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2445.0304</v>
+        <v>2323.611392</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.58</v>
+        <v>10.17</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3131.228928</v>
+        <v>3009.886464</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2802.961152</v>
+        <v>2681.618688</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>10.04</v>
+        <v>9.43</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2220.91136</v>
+        <v>2085.975552</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2148.627456</v>
+        <v>2013.69152</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.3</v>
+        <v>36.13</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5372.548608</v>
+        <v>5204.026368</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.8599634</v>
+        <v>4.838549</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5286.621184</v>
+        <v>5118.098944</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.2</v>
+        <v>4.88</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>883.24736</v>
+        <v>828.893696</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>746.969664</v>
+        <v>692.620544</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-15 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-16 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.25</v>
+        <v>16.09</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42.33</v>
+        <v>43.77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34.11</v>
+        <v>34.75</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.9</v>
+        <v>15.56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.98</v>
+        <v>15.41</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.17</v>
+        <v>10.54</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.13</v>
+        <v>36.84</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.88</v>
+        <v>5.19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>56.22</v>
+        <v>57.31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-15 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-16 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.25</v>
+        <v>16.09</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7519.483904</v>
+        <v>7933.671936</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7008.84224</v>
+        <v>7422.88384</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>42.33</v>
+        <v>43.77</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17550.780416</v>
+        <v>18147.82976</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>16792.742912</v>
+        <v>17393.328128</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34.11</v>
+        <v>34.75</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25135.439872</v>
+        <v>25607.051264</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23967.731712</v>
+        <v>24955.168768</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.9</v>
+        <v>15.56</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9993.614336000001</v>
+        <v>10452.717568</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9545.525248</v>
+        <v>9988.892672</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.98</v>
+        <v>15.41</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15398.465536</v>
+        <v>15840.478208</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15059.34848</v>
+        <v>15501.360128</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2318.811136</v>
+        <v>2455.037696</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2323.611392</v>
+        <v>2459.837696</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.17</v>
+        <v>10.54</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3009.886464</v>
+        <v>3119.39072</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2681.618688</v>
+        <v>2791.122944</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.43</v>
+        <v>9.76</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2085.975552</v>
+        <v>2158.973696</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2013.69152</v>
+        <v>2086.689536</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>36.13</v>
+        <v>36.84</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5204.026368</v>
+        <v>5306.292224</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.838549</v>
+        <v>4.837036</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5118.098944</v>
+        <v>5220.364288</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>4.88</v>
+        <v>5.19</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>828.893696</v>
+        <v>881.5488</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>692.620544</v>
+        <v>745.2712320000001</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-16 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-17 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.09</v>
+        <v/>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43.77</v>
+        <v/>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,7 +637,7 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34.75</v>
+        <v>35.53</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15.56</v>
+        <v/>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>15.41</v>
+        <v/>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v/>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.54</v>
+        <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.84</v>
+        <v>37.64</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.19</v>
+        <v/>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.31</v>
+        <v>57.13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-16 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-17 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.09</v>
+        <v>15.98</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7933.671936</v>
+        <v>7879.432704</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7422.88384</v>
+        <v>7368.664064</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>43.77</v>
+        <v>44.21</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18147.82976</v>
+        <v>18330.261504</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17393.328128</v>
+        <v>17576.841216</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>34.75</v>
+        <v>35.53</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25607.051264</v>
+        <v>26181.82656</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>24955.168768</v>
+        <v>25812.914176</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.56</v>
+        <v>15.3</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10452.717568</v>
+        <v>10278.05696</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9988.892672</v>
+        <v>9814.233088000001</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.41</v>
+        <v>15.47</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15840.478208</v>
+        <v>15902.154752</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15501.360128</v>
+        <v>15563.036672</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.289999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2455.037696</v>
+        <v>2440.2304</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2459.837696</v>
+        <v>2445.0304</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.54</v>
+        <v>10.71</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3119.39072</v>
+        <v>3169.703424</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2791.122944</v>
+        <v>2841.435648</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.76</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2158.973696</v>
+        <v>2163.397632</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2086.689536</v>
+        <v>2091.113728</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>36.84</v>
+        <v>37.64</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5306.292224</v>
+        <v>5421.520896</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.837036</v>
+        <v>4.830445</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5220.364288</v>
+        <v>5335.593472</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.19</v>
+        <v>5.33</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>881.5488</v>
+        <v>905.328576</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>745.2712320000001</v>
+        <v>769.049024</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-17 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-20 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.53</v>
+        <v>35.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.64</v>
+        <v>37.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.13</v>
+        <v>57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-17 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-20 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.21</v>
+        <v>44.43</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18330.261504</v>
+        <v>18421.477376</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17576.841216</v>
+        <v>17668.59776</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.53</v>
+        <v>35.8</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26181.82656</v>
+        <v>26380.78976</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25812.914176</v>
+        <v>25154.12992</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.3</v>
+        <v>15.05</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10278.05696</v>
+        <v>10110.114816</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9814.233088000001</v>
+        <v>9646.290944</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.47</v>
+        <v>15.33</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15902.154752</v>
+        <v>15758.242816</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15563.036672</v>
+        <v>15419.12576</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.24</v>
+        <v>8.26</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2440.2304</v>
+        <v>2446.153472</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2445.0304</v>
+        <v>2450.953472</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.71</v>
+        <v>10.59</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3169.703424</v>
+        <v>3134.188544</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2841.435648</v>
+        <v>2805.920768</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2163.397632</v>
+        <v>2161.185792</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2091.113728</v>
+        <v>2088.901632</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.64</v>
+        <v>37.4</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5421.520896</v>
+        <v>5386.952704</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.830445</v>
+        <v>4.8058186</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5335.593472</v>
+        <v>5301.024768</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.33</v>
+        <v>5.21</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>905.328576</v>
+        <v>884.94592</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>769.049024</v>
+        <v>748.668096</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-20 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-21 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.8</v>
+        <v>36.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.4</v>
+        <v>36.91</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57</v>
+        <v>58.08</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-20 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-21 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.98</v>
+        <v>15.99</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7879.432704</v>
+        <v>7884.363264</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7368.664064</v>
+        <v>7373.593088</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.43</v>
+        <v>44.29</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18421.477376</v>
+        <v>18363.430912</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17668.59776</v>
+        <v>17610.207232</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>35.8</v>
+        <v>36.7</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>26380.78976</v>
+        <v>27043.9936</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25154.12992</v>
+        <v>25817.335808</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.05</v>
+        <v>15.02</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10110.114816</v>
+        <v>10089.962496</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9646.290944</v>
+        <v>9626.1376</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.33</v>
+        <v>15.13</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15758.242816</v>
+        <v>15552.656384</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15419.12576</v>
+        <v>15213.538304</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2446.153472</v>
+        <v>2428.384768</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2450.953472</v>
+        <v>2433.184768</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.59</v>
+        <v>10.39</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3134.188544</v>
+        <v>3074.997248</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2805.920768</v>
+        <v>2746.729216</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.77</v>
+        <v>9.26</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2161.185792</v>
+        <v>2048.370432</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2088.901632</v>
+        <v>1976.0864</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.4</v>
+        <v>36.91</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5386.952704</v>
+        <v>5316.374528</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.8058186</v>
+        <v>4.800442</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5301.024768</v>
+        <v>5230.447104</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>884.94592</v>
+        <v>881.5488</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>748.668096</v>
+        <v>745.2712320000001</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-21 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-22 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.91</v>
+        <v>37.32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.08</v>
+        <v>57.47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-21 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-22 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.99</v>
+        <v>16.09</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7884.363264</v>
+        <v>7933.671936</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7373.593088</v>
+        <v>7422.88384</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>44.29</v>
+        <v>43.65</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18363.430912</v>
+        <v>18098.075648</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17610.207232</v>
+        <v>17343.279104</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5074,7 +5074,7 @@
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>25817.335808</v>
+        <v>24240.381952</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.02</v>
+        <v>15.14</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10089.962496</v>
+        <v>10170.574848</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9626.1376</v>
+        <v>9706.749952</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2428.384768</v>
+        <v>2460.960768</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2433.184768</v>
+        <v>2465.760512</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.39</v>
+        <v>10.34</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3074.997248</v>
+        <v>3060.199424</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2746.729216</v>
+        <v>2731.931392</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.26</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2048.370432</v>
+        <v>2070.49088</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1976.0864</v>
+        <v>1998.207104</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>36.91</v>
+        <v>37.32</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5316.374528</v>
+        <v>5375.429632</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.800442</v>
+        <v>4.787173</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5230.447104</v>
+        <v>5289.501696</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>881.5488</v>
+        <v>884.94592</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>745.2712320000001</v>
+        <v>748.668096</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-22 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-23 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>36.7</v>
+        <v>33.98</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>37.32</v>
+        <v>33.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.47</v>
+        <v>54.51</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-22 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-23 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>16.09</v>
+        <v>15.12</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7933.671936</v>
+        <v>7455.38304</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7422.88384</v>
+        <v>6944.764416</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>43.65</v>
+        <v>41.07</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>18098.075648</v>
+        <v>17028.360192</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>17343.279104</v>
+        <v>16267.229184</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>36.7</v>
+        <v>33.98</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27043.9936</v>
+        <v>25039.642624</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>24240.381952</v>
+        <v>23275.051008</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>15.14</v>
+        <v>14.11</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10170.574848</v>
+        <v>9478.652928</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9706.749952</v>
+        <v>9014.829056</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>15.13</v>
+        <v>13.88</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>15552.656384</v>
+        <v>14267.737088</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>15213.538304</v>
+        <v>13928.620032</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8.31</v>
+        <v>7.65</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2460.960768</v>
+        <v>2265.50528</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2465.760512</v>
+        <v>2270.30528</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>10.34</v>
+        <v>9.52</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3060.199424</v>
+        <v>2817.51424</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2731.931392</v>
+        <v>2489.246208</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>9.359999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2070.49088</v>
+        <v>1906.798336</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1998.207104</v>
+        <v>1834.514432</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37.32</v>
+        <v>33.4</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5375.429632</v>
+        <v>4810.807808</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.787173</v>
+        <v>4.7789574</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5289.501696</v>
+        <v>4724.879872</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>5.21</v>
+        <v>4.77</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>884.94592</v>
+        <v>810.2096</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>748.668096</v>
+        <v>673.937984</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-23 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-24 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -614,7 +614,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.98</v>
+        <v>31.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>33.4</v>
+        <v>33.29</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -830,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>54.51</v>
+        <v>53.96</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-23 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-24 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.12</v>
+        <v>14.77</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7455.38304</v>
+        <v>7282.805248</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>6944.764416</v>
+        <v>6772.24704</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>41.07</v>
+        <v>40.15</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17028.360192</v>
+        <v>16646.913024</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>16267.229184</v>
+        <v>15883.521024</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>33.98</v>
+        <v>31.35</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>25039.642624</v>
+        <v>23101.61408</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23275.051008</v>
+        <v>21653.88288</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.11</v>
+        <v>13.85</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9478.652928</v>
+        <v>9289.366528</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9014.829056</v>
+        <v>8840.168448</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>13.88</v>
+        <v>13.45</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>14267.737088</v>
+        <v>13825.72544</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>13928.620032</v>
+        <v>13486.60736</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.65</v>
+        <v>7.47</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2265.50528</v>
+        <v>2212.199168</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2270.30528</v>
+        <v>2216.999168</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.52</v>
+        <v>9.18</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2817.51424</v>
+        <v>2716.888832</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2489.246208</v>
+        <v>2388.6208</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1906.798336</v>
+        <v>1866.98112</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1834.514432</v>
+        <v>1794.697216</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>33.4</v>
+        <v>33.29</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4810.807808</v>
+        <v>4794.963968</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7789574</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4724.879872</v>
+        <v>4709.036032</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>4.77</v>
+        <v>4.64</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>810.2096</v>
+        <v>788.128384</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>673.937984</v>
+        <v>651.858688</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-24 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-27 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v/>
+        <v>14.85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v/>
+        <v>40.32</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>31.35</v>
+        <v>31.03</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v/>
+        <v>13.98</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v/>
+        <v>13.64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v/>
+        <v>7.49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v/>
+        <v>9.300000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v/>
+        <v>8.220000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>33.29</v>
+        <v>33.43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v/>
+        <v>4.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>53.96</v>
+        <v>53.91</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-24 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-27 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>14.77</v>
+        <v>14.85</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7282.805248</v>
+        <v>7322.251264</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>6772.24704</v>
+        <v>6811.679744</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>40.15</v>
+        <v>40.32</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>16646.913024</v>
+        <v>16717.396992</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>15883.521024</v>
+        <v>15954.423808</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>31.35</v>
+        <v>31.03</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>23101.61408</v>
+        <v>22865.80736</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>21653.88288</v>
+        <v>22276.558848</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>13.85</v>
+        <v>13.98</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9289.366528</v>
+        <v>9391.322112</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>8840.168448</v>
+        <v>8927.498240000001</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>13.45</v>
+        <v>13.64</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>13825.72544</v>
+        <v>14021.03296</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>13486.60736</v>
+        <v>13681.91488</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.47</v>
+        <v>7.49</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2212.199168</v>
+        <v>2218.121984</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2216.999168</v>
+        <v>2222.92224</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.18</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2716.888832</v>
+        <v>2752.403712</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2388.6208</v>
+        <v>2424.13568</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.44</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1866.98112</v>
+        <v>1818.315904</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1794.697216</v>
+        <v>1746.031872</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>33.29</v>
+        <v>33.43</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4794.963968</v>
+        <v>4815.129088</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7789574</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4709.036032</v>
+        <v>4729.201152</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>788.128384</v>
+        <v>781.334208</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>651.858688</v>
+        <v>645.065024</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-28 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>14.85</v>
+        <v>15.64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>40.32</v>
+        <v>41.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>31.03</v>
+        <v>32.16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13.98</v>
+        <v>14.62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>13.64</v>
+        <v>14.21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.49</v>
+        <v>7.82</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>33.43</v>
+        <v>35</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.6</v>
+        <v>4.82</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>53.91</v>
+        <v>54.42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-27 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-28 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>14.85</v>
+        <v>15.64</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7322.251264</v>
+        <v>7711.785472</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>6811.679744</v>
+        <v>7201.075712</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>40.32</v>
+        <v>41.66</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>16717.396992</v>
+        <v>17272.9856</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>15954.423808</v>
+        <v>16513.302528</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>31.03</v>
+        <v>31.9</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>22865.80736</v>
+        <v>23506.905088</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>22276.558848</v>
+        <v>22471.835648</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>13.98</v>
+        <v>14.62</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9391.322112</v>
+        <v>9805.814784</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>8927.498240000001</v>
+        <v>9357.430784</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>13.64</v>
+        <v>14.21</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>14021.03296</v>
+        <v>14606.956544</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>13681.91488</v>
+        <v>14267.838464</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.49</v>
+        <v>7.82</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2218.121984</v>
+        <v>2315.849984</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2222.92224</v>
+        <v>2320.649728</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2752.403712</v>
+        <v>2829.352704</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2424.13568</v>
+        <v>2501.084672</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.220000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1818.315904</v>
+        <v>1906.798336</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1746.031872</v>
+        <v>1834.514432</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>33.43</v>
+        <v>35</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4815.129088</v>
+        <v>5041.265664</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7789574</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4729.201152</v>
+        <v>4955.337728</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>4.6</v>
+        <v>4.82</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>781.334208</v>
+        <v>818.7024</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>645.065024</v>
+        <v>682.43008</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-28 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-29 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.64</v>
+        <v>15.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>41.66</v>
+        <v>41.95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>32.16</v>
+        <v>31.85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.62</v>
+        <v>14.92</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.21</v>
+        <v>14.42</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.82</v>
+        <v>7.97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.56</v>
+        <v>9.65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>35</v>
+        <v>35.33</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>54.42</v>
+        <v>53.86</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-28 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-29 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.64</v>
+        <v>15.8</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7711.785472</v>
+        <v>7790.678016</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7201.075712</v>
+        <v>7279.940608</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>41.66</v>
+        <v>41.95</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17272.9856</v>
+        <v>17393.225728</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>16513.302528</v>
+        <v>16634.254336</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>31.9</v>
+        <v>31.85</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>23506.905088</v>
+        <v>23470.05952</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>22471.835648</v>
+        <v>22144.65536</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.62</v>
+        <v>14.92</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9805.814784</v>
+        <v>10022.785024</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9357.430784</v>
+        <v>9558.961152</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.21</v>
+        <v>14.42</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>14606.956544</v>
+        <v>14822.822912</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>14267.838464</v>
+        <v>14483.704832</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.82</v>
+        <v>7.97</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2315.849984</v>
+        <v>2360.27136</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2320.649728</v>
+        <v>2365.071616</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.56</v>
+        <v>9.65</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2829.352704</v>
+        <v>2855.98848</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2501.084672</v>
+        <v>2527.720704</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1906.798336</v>
+        <v>1904.58624</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1834.514432</v>
+        <v>1832.302336</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>35</v>
+        <v>35.33</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5041.265664</v>
+        <v>5088.797696</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7789574</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4955.337728</v>
+        <v>5002.86976</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>818.7024</v>
+        <v>813.60672</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>682.43008</v>
+        <v>677.334848</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-30 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.8</v>
+        <v>15.33</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>41.95</v>
+        <v>40.75</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>31.85</v>
+        <v>31.75</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.92</v>
+        <v>14.45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.42</v>
+        <v>14.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.97</v>
+        <v>7.76</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.65</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8.609999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>35.33</v>
+        <v>34.15</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.79</v>
+        <v>4.61</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>53.86</v>
+        <v>51.49</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-29 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-30 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.8</v>
+        <v>15.33</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7790.678016</v>
+        <v>7558.92992</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7279.940608</v>
+        <v>7048.274944</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>41.95</v>
+        <v>40.75</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>17393.225728</v>
+        <v>16895.68256</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>16634.254336</v>
+        <v>16133.76512</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>31.85</v>
+        <v>31.72</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>23470.05952</v>
+        <v>23374.26432</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>22144.65536</v>
+        <v>22169.708544</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.92</v>
+        <v>14.45</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10022.785024</v>
+        <v>9691.793408</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9558.961152</v>
+        <v>9243.230208000001</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.42</v>
+        <v>14.04</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>14822.822912</v>
+        <v>14432.206848</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>14483.704832</v>
+        <v>14093.089792</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.97</v>
+        <v>7.76</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2360.27136</v>
+        <v>2298.08128</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2365.071616</v>
+        <v>2302.88128</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.65</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2855.98848</v>
+        <v>2773.120512</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2527.720704</v>
+        <v>2444.852736</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.609999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1904.58624</v>
+        <v>1836.012416</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1832.302336</v>
+        <v>1763.728384</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>35.33</v>
+        <v>34.15</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5088.797696</v>
+        <v>4918.8352</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7789574</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5002.86976</v>
+        <v>4832.907264</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>4.79</v>
+        <v>4.61</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>813.60672</v>
+        <v>783.032768</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>677.334848</v>
+        <v>646.763456</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>

--- a/02-data-engine/comps_workbook.xlsx
+++ b/02-data-engine/comps_workbook.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
+          <t>Generated 2026-10-31 by metals_engine.py. To refresh: open a terminal in this folder and run:  python metals_engine.py</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
         <v>6.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.33</v>
+        <v>14.26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F2" s="4">
@@ -610,11 +610,11 @@
         <v>22.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>40.75</v>
+        <v>37.98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -637,11 +637,11 @@
         <v>7.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>31.75</v>
+        <v>29.97</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F4" s="4">
@@ -664,11 +664,11 @@
         <v>5.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.45</v>
+        <v>13.53</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -691,11 +691,11 @@
         <v>6.62</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.04</v>
+        <v>13.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F6" s="4">
@@ -718,11 +718,11 @@
         <v>4.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7.76</v>
+        <v>7.21</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -745,11 +745,11 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F8" s="4">
@@ -772,11 +772,11 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F9" s="4">
@@ -799,11 +799,11 @@
         <v>12.76</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>34.15</v>
+        <v>32.13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F10" s="4">
@@ -826,11 +826,11 @@
         <v>1.14</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.61</v>
+        <v>4.34</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -853,11 +853,11 @@
         <v>30.91</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>51.49</v>
+        <v>49.13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F12" s="4">
@@ -4932,7 +4932,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Snapshot 2026-10-30 — listed-currency figures from Yahoo Finance</t>
+          <t>Snapshot 2026-10-31 — listed-currency figures from Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>15.33</v>
+        <v>14.26</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7558.92992</v>
+        <v>7031.333888</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>6.02</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>7048.274944</v>
+        <v>6520.864768</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>942.211968</v>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>40.75</v>
+        <v>37.98</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>16895.68256</v>
+        <v>15747.190784</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>17.642</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>16133.76512</v>
+        <v>14978.470912</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>2124</v>
@@ -5065,16 +5065,16 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>31.72</v>
+        <v>29.97</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>23374.26432</v>
+        <v>22084.70016</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>6.95</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>22169.708544</v>
+        <v>20858.038272</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>4027.734016</v>
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14.45</v>
+        <v>13.53</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9691.793408</v>
+        <v>9089.027072000001</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>3.986</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>9243.230208000001</v>
+        <v>8625.2032</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>969.484992</v>
@@ -5135,16 +5135,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14.04</v>
+        <v>13.1</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>14432.206848</v>
+        <v>13465.94816</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>10.121</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>14093.089792</v>
+        <v>13126.83008</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1629.442048</v>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7.76</v>
+        <v>7.21</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2298.08128</v>
+        <v>2135.201664</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2.406</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2302.88128</v>
+        <v>2140.001664</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>281.5</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9.369999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2773.120512</v>
+        <v>2628.101632</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.97</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2444.852736</v>
+        <v>2299.8336</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>750.460032</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.300000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1836.012416</v>
+        <v>1760.802176</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.461</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1763.728384</v>
+        <v>1688.518272</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>309.139008</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>34.15</v>
+        <v>32.13</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4918.8352</v>
+        <v>4627.881984</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.7789574</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4832.907264</v>
+        <v>4541.954048</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>207.972992</v>
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>4.61</v>
+        <v>4.34</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>783.032768</v>
+        <v>737.17184</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1.664</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>646.763456</v>
+        <v>600.906304</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>57.053</v>
